--- a/BOM/Lineux Stealth r2t Bom.xlsx
+++ b/BOM/Lineux Stealth r2t Bom.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="80">
   <si>
     <t>Lineux Stealth r2t Bill Of Material</t>
   </si>
@@ -136,7 +136,7 @@
     <t>for klicky</t>
   </si>
   <si>
-    <t>m3 x 8mm bhcs</t>
+    <t>m3 x 6mm bhcs</t>
   </si>
   <si>
     <t>m3 x 12mm shcs</t>
@@ -210,9 +210,6 @@
   </si>
   <si>
     <t>Lineux r2t Dock</t>
-  </si>
-  <si>
-    <t>m3 x 6mm bhcs</t>
   </si>
   <si>
     <t>m3 x 10mm bhcs</t>
@@ -2334,7 +2331,7 @@
       <c r="Z48" s="4"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="18" t="s">
         <v>41</v>
       </c>
       <c r="B49" s="17">
@@ -3129,7 +3126,7 @@
     </row>
     <row r="73">
       <c r="A73" s="9" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B73" s="19">
         <v>1.0</v>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="74">
       <c r="A74" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B74" s="19">
         <v>2.0</v>
@@ -3193,7 +3190,7 @@
     </row>
     <row r="75">
       <c r="A75" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B75" s="19">
         <v>1.0</v>
@@ -3225,7 +3222,7 @@
     </row>
     <row r="76">
       <c r="A76" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B76" s="19">
         <v>4.0</v>
@@ -3257,7 +3254,7 @@
     </row>
     <row r="77">
       <c r="A77" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B77" s="19">
         <v>4.0</v>
@@ -3355,7 +3352,7 @@
     </row>
     <row r="80">
       <c r="A80" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B80" s="19">
         <v>1.0</v>
@@ -3389,13 +3386,13 @@
     </row>
     <row r="81">
       <c r="A81" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B81" s="19">
         <v>1.0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>19</v>
@@ -3425,13 +3422,13 @@
     </row>
     <row r="82">
       <c r="A82" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" s="19">
         <v>1.0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D82" s="28" t="s">
         <v>19</v>
@@ -3461,13 +3458,13 @@
     </row>
     <row r="83">
       <c r="A83" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B83" s="19">
         <v>1.0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>19</v>
@@ -3525,7 +3522,7 @@
     </row>
     <row r="85">
       <c r="A85" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>8</v>
@@ -3563,13 +3560,13 @@
     </row>
     <row r="86">
       <c r="A86" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B86" s="19">
         <v>1.0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D86" s="20" t="s">
         <v>19</v>
@@ -3599,13 +3596,13 @@
     </row>
     <row r="87">
       <c r="A87" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B87" s="19">
         <v>1.0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="10"/>
@@ -3633,13 +3630,13 @@
     </row>
     <row r="88">
       <c r="A88" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B88" s="19">
         <v>1.0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="10"/>
@@ -3667,17 +3664,17 @@
     </row>
     <row r="89">
       <c r="A89" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B89" s="19">
         <v>1.0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
